--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V163"/>
+  <dimension ref="A1:V166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16402,10 +16402,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A163" t="n">
+        <v>1101</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -16457,7 +16455,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N163" s="2" t="n">
+      <c r="N163" s="1" t="n">
         <v>38205</v>
       </c>
       <c r="O163" t="inlineStr">
@@ -16492,6 +16490,296 @@
         </is>
       </c>
       <c r="V163" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>116650</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>INGENIERIA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>135</v>
+      </c>
+      <c r="J164" t="n">
+        <v>8</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>45274</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>4071</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>BACTERIOLOGIA</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>176</v>
+      </c>
+      <c r="J165" t="n">
+        <v>10</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>6506185</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Tecnología de diagnóstico y tratamiento médico</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Bacteriología</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INTERNACIONAL DEL TRÓPICO AMERICANO - UNITRÓPICO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>116114</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>154</v>
+      </c>
+      <c r="J166" t="n">
+        <v>9</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>45105</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V166"/>
+  <dimension ref="A1:V167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16496,10 +16496,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A164" t="n">
+        <v>1709</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -16551,7 +16549,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N164" s="1" t="n">
         <v>45274</v>
       </c>
       <c r="O164" t="inlineStr">
@@ -16592,10 +16590,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A165" t="n">
+        <v>1724</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -16649,7 +16645,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N165" s="2" t="n">
+      <c r="N165" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O165" t="inlineStr">
@@ -16690,10 +16686,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
+      <c r="A166" t="n">
+        <v>2743</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -16745,7 +16739,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N166" s="2" t="n">
+      <c r="N166" s="1" t="n">
         <v>45105</v>
       </c>
       <c r="O166" t="inlineStr">
@@ -16780,6 +16774,104 @@
         </is>
       </c>
       <c r="V166" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>103928</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN DISEÑO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>180</v>
+      </c>
+      <c r="J167" t="n">
+        <v>10</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1449066</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>41990</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V167"/>
+  <dimension ref="A1:V169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16780,10 +16780,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A167" t="n">
+        <v>3302</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -16837,7 +16835,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N167" s="2" t="n">
+      <c r="N167" s="1" t="n">
         <v>41990</v>
       </c>
       <c r="O167" t="inlineStr">
@@ -16872,6 +16870,202 @@
         </is>
       </c>
       <c r="V167" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DE POPAYAN</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>106807</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>COMUNICACIÖN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>154</v>
+      </c>
+      <c r="J168" t="n">
+        <v>9</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>5571296</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>43203</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA LUMEN GENTIUM - UNICATÓLICA - CALI</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>106813</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>MERCADEO</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>162</v>
+      </c>
+      <c r="J169" t="n">
+        <v>9</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>3613829</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>43212</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V169"/>
+  <dimension ref="A1:V170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16876,10 +16876,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
+      <c r="A168" t="n">
+        <v>2715</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -16933,7 +16931,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N168" s="2" t="n">
+      <c r="N168" s="1" t="n">
         <v>43203</v>
       </c>
       <c r="O168" t="inlineStr">
@@ -16974,10 +16972,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
+      <c r="A169" t="n">
+        <v>2731</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -17031,7 +17027,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N169" s="2" t="n">
+      <c r="N169" s="1" t="n">
         <v>43212</v>
       </c>
       <c r="O169" t="inlineStr">
@@ -17066,6 +17062,102 @@
         </is>
       </c>
       <c r="V169" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>116188</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN HIGIENE Y SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>155</v>
+      </c>
+      <c r="J170" t="n">
+        <v>10</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>45189</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V170"/>
+  <dimension ref="A1:V173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17068,10 +17068,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A170" t="n">
+        <v>1704</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -17123,7 +17121,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N170" s="1" t="n">
         <v>45189</v>
       </c>
       <c r="O170" t="inlineStr">
@@ -17158,6 +17156,300 @@
         </is>
       </c>
       <c r="V170" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>52363</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>COMUNICACION SOCIAL Y PERIODISMO</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>144</v>
+      </c>
+      <c r="J171" t="n">
+        <v>8</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>10034460</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>45365</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>105468</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>DISEÑO Y GESTIÓN DEL PRODUCTO</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>142</v>
+      </c>
+      <c r="J172" t="n">
+        <v>8</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>8587000</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>45104</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA HORIZONTE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>107213</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>164</v>
+      </c>
+      <c r="J173" t="n">
+        <v>10</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>5826000</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>43307</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V173"/>
+  <dimension ref="A1:V174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17162,10 +17162,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
+      <c r="A171" t="n">
+        <v>1723</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -17219,7 +17217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N171" s="2" t="n">
+      <c r="N171" s="1" t="n">
         <v>45365</v>
       </c>
       <c r="O171" t="inlineStr">
@@ -17260,10 +17258,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A172" t="n">
+        <v>1812</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -17317,7 +17313,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N172" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="O172" t="inlineStr">
@@ -17358,10 +17354,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>4721</t>
-        </is>
+      <c r="A173" t="n">
+        <v>4721</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -17415,7 +17409,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N173" s="2" t="n">
+      <c r="N173" s="1" t="n">
         <v>43307</v>
       </c>
       <c r="O173" t="inlineStr">
@@ -17450,6 +17444,102 @@
         </is>
       </c>
       <c r="V173" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>108783</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>MATEMATICAS Y CIENCIAS DE LA COMPUTACION</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>150</v>
+      </c>
+      <c r="J174" t="n">
+        <v>9</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>43826</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V174"/>
+  <dimension ref="A1:V177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17450,10 +17450,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A174" t="n">
+        <v>2805</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -17505,7 +17503,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N174" s="2" t="n">
+      <c r="N174" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="O174" t="inlineStr">
@@ -17540,6 +17538,296 @@
         </is>
       </c>
       <c r="V174" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pueblo Rico</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>117436</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LITERATURA Y LENGUA CASTELLANA</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>159</v>
+      </c>
+      <c r="J175" t="n">
+        <v>10</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>43704</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>15706</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ECONOMIA</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>143</v>
+      </c>
+      <c r="J176" t="n">
+        <v>9</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>107747</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN DANZA Y PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>144</v>
+      </c>
+      <c r="J177" t="n">
+        <v>8</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>5189545</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>43558</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Bellas artes</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V177"/>
+  <dimension ref="A1:V182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17544,10 +17544,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A175" t="n">
+        <v>1111</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -17599,7 +17597,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N175" s="1" t="n">
         <v>43704</v>
       </c>
       <c r="O175" t="inlineStr">
@@ -17640,10 +17638,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A176" t="n">
+        <v>1709</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -17695,7 +17691,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N176" s="1" t="n">
         <v>45906</v>
       </c>
       <c r="O176" t="inlineStr">
@@ -17736,10 +17732,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A177" t="n">
+        <v>1716</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -17793,7 +17787,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N177" s="2" t="n">
+      <c r="N177" s="1" t="n">
         <v>43558</v>
       </c>
       <c r="O177" t="inlineStr">
@@ -17828,6 +17822,494 @@
         </is>
       </c>
       <c r="V177" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>109144</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>CIENCIA DE DATOS Y SIMULACIÓN COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>125</v>
+      </c>
+      <c r="J178" t="n">
+        <v>8</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>108578</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>144</v>
+      </c>
+      <c r="J179" t="n">
+        <v>9</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>12273435</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>43809</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>15613</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>PERIODISMO Y OPINION PUBLICA</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>155</v>
+      </c>
+      <c r="J180" t="n">
+        <v>9</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>16667415</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>37326</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>5505</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>COMUNICACION SOCIAL Y PERIODISMO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>128</v>
+      </c>
+      <c r="J181" t="n">
+        <v>8</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>4799300</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>45119</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>108754</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION DE EMPRESAS TURISTICA</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>156</v>
+      </c>
+      <c r="J182" t="n">
+        <v>10</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>5956780</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>43847</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V182"/>
+  <dimension ref="A1:V183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17828,10 +17828,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A178" t="n">
+        <v>1707</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -17883,7 +17881,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N178" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O178" t="inlineStr">
@@ -17924,10 +17922,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A179" t="n">
+        <v>1710</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -17981,7 +17977,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N179" s="2" t="n">
+      <c r="N179" s="1" t="n">
         <v>43809</v>
       </c>
       <c r="O179" t="inlineStr">
@@ -18022,10 +18018,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A180" t="n">
+        <v>1714</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -18079,7 +18073,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N180" s="2" t="n">
+      <c r="N180" s="1" t="n">
         <v>37326</v>
       </c>
       <c r="O180" t="inlineStr">
@@ -18120,10 +18114,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
+      <c r="A181" t="n">
+        <v>1733</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -18177,7 +18169,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N181" s="2" t="n">
+      <c r="N181" s="1" t="n">
         <v>45119</v>
       </c>
       <c r="O181" t="inlineStr">
@@ -18218,10 +18210,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
+      <c r="A182" t="n">
+        <v>1827</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -18275,7 +18265,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N182" s="2" t="n">
+      <c r="N182" s="1" t="n">
         <v>43847</v>
       </c>
       <c r="O182" t="inlineStr">
@@ -18310,6 +18300,104 @@
         </is>
       </c>
       <c r="V182" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>104235</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>CONTADURÍA INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>144</v>
+      </c>
+      <c r="J183" t="n">
+        <v>9</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>26860000</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>42048</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>

--- a/data/novedades/Inactivos_pregrado.xlsx
+++ b/data/novedades/Inactivos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V183"/>
+  <dimension ref="A1:V188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18306,10 +18306,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A183" t="n">
+        <v>1813</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -18363,7 +18361,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N183" s="2" t="n">
+      <c r="N183" s="1" t="n">
         <v>42048</v>
       </c>
       <c r="O183" t="inlineStr">
@@ -18398,6 +18396,492 @@
         </is>
       </c>
       <c r="V183" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>105016</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>158</v>
+      </c>
+      <c r="J184" t="n">
+        <v>9</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>4660000</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>42292</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>10569</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>CONTADURIA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>158</v>
+      </c>
+      <c r="J185" t="n">
+        <v>9</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>3205000</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>36754</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>54359</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>DISEÑO DE MODAS</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>144</v>
+      </c>
+      <c r="J186" t="n">
+        <v>8</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>39840</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>103230</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE MINAS</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>170</v>
+      </c>
+      <c r="J187" t="n">
+        <v>10</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>41752</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Minería y extracción</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Ingeniería de minas, metalurgia y afines</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>FUNDACION DE EDUCACION SUPERIOR SAN JOSE -FESSANJOSE-</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>105348</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>158</v>
+      </c>
+      <c r="J188" t="n">
+        <v>9</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>4370822</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>42418</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
         <is>
           <t>Inactivo</t>
         </is>
